--- a/Extracted_data_analysis/temperate/Output-Transformed_data/sampling_unit_tot.xlsx
+++ b/Extracted_data_analysis/temperate/Output-Transformed_data/sampling_unit_tot.xlsx
@@ -425,7 +425,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3">
@@ -447,7 +447,7 @@
         <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5">
